--- a/output/pdf_financials_xlsx/REC.xlsx
+++ b/output/pdf_financials_xlsx/REC.xlsx
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001599</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000315</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1849,10 +1849,10 @@
         <v>-0.147492</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.150539</v>
+        <v>-0.152138</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.254519</v>
+        <v>-0.254834</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.456538</v>
@@ -1955,10 +1955,10 @@
         <v>-0.147492</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.150539</v>
+        <v>-0.152138</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.254519</v>
+        <v>-0.254834</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.456538</v>
@@ -2225,16 +2225,16 @@
         <v>0.356342</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.17203</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.487717</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.041739</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.008335</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000924</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.052255</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000505</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.039436</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.003501</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.002435</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.005487</v>
       </c>
     </row>
     <row r="35">
@@ -2327,16 +2327,16 @@
         <v>0.356342</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.17203</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.487717</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.041739</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.008335</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2344,25 +2344,25 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000924</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.052255</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000505</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.039436</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.003501</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.002435</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.005487</v>
       </c>
     </row>
     <row r="37">
@@ -2939,16 +2939,16 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.17203</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.487717</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.041739</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008335</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.000924</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.052255</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.000505</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.040936</v>
+        <v>0.0015</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.003501</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.002435</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.005487</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -29912,11 +29912,7 @@
           <t>General and administrative fees</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" s="5" t="n">
         <v>0.000549</v>
       </c>

--- a/output/pdf_financials_xlsx/REC.xlsx
+++ b/output/pdf_financials_xlsx/REC.xlsx
@@ -6692,13 +6692,13 @@
         <v>0</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>0.051079</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>0.046655</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>0.432592</v>
       </c>
     </row>
     <row r="121">
@@ -13068,7 +13068,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/REC.xlsx
+++ b/output/pdf_financials_xlsx/REC.xlsx
@@ -1493,11 +1493,15 @@
       <c r="J20" s="3" t="n">
         <v>-0.108683</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>0.040281</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.293966</v>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.773524</v>
@@ -1547,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>0.099907</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>9e-06</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -5712,7 +5716,7 @@
         <v>-0.001396</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.011439</v>
       </c>
       <c r="M101" s="3" t="n">
         <v>0</v>
@@ -5967,7 +5971,7 @@
         <v>-0.016978</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.037519</v>
+        <v>-0.02608</v>
       </c>
       <c r="M106" s="3" t="n">
         <v>0.027472</v>
@@ -6145,16 +6149,16 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.003335</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.003613</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.001587</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.001643</v>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
@@ -6162,10 +6166,10 @@
         </is>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.001682</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.001278</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -14070,7 +14074,11 @@
           <t>Provision on GST receivable</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -15786,7 +15794,11 @@
           <t>Accretion (Note 6)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -16384,7 +16396,11 @@
           <t>Accretion (Note 6)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -17754,7 +17770,11 @@
           <t>Accretion (Note 7)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -18010,7 +18030,11 @@
           <t>Proceeds from share issuance (Note 9)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -18442,7 +18466,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -22276,7 +22304,11 @@
           <t>Income from discontinued operations</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -23560,11 +23592,7 @@
           <t>Income from continued operations</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
